--- a/Employee task3_Details.xlsx
+++ b/Employee task3_Details.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAJASHREE KANNAYERAM\Documents\jaya project in excel\EXCEL CODING CHALLANGE IN GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E57089-B1C7-4F99-8CC1-9F9DDCA2C884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5449F2E3-5E46-4EC0-8F2E-2B6D1E568B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="table" sheetId="1" r:id="rId1"/>
-    <sheet name="observation task3" sheetId="3" r:id="rId2"/>
+    <sheet name="table1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="300">
   <si>
     <t>Employee ID</t>
   </si>
@@ -877,9 +877,6 @@
     <t>user30@example.com</t>
   </si>
   <si>
-    <t>observation</t>
-  </si>
-  <si>
     <t>SALARY</t>
   </si>
   <si>
@@ -904,28 +901,37 @@
     <t>METRICS</t>
   </si>
   <si>
-    <t>2.the average salary is 66280.93</t>
-  </si>
-  <si>
-    <t>3.the minimum salary is 30280 and the maximum salary is 99621</t>
-  </si>
-  <si>
-    <t>4.the total performance rating score is 359</t>
-  </si>
-  <si>
-    <t>5.the average performance rating score is 2.872</t>
-  </si>
-  <si>
-    <t>6.the minimum performance rating is 1 and the maximum performance rating is 5</t>
-  </si>
-  <si>
-    <t>8.the difference in count indicates that some performance rating values are missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.there are 142 salary records and 125 performance rating records available in the dataset </t>
-  </si>
-  <si>
-    <t>1.the total salary of all employees is 9411892</t>
+    <t>OBSERVATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 TOTAL SALARY OF EMPLOYEES</t>
+  </si>
+  <si>
+    <t>3 MINIMUM SALARY OF EMPLOYEES</t>
+  </si>
+  <si>
+    <t>4 MAXIMUM SALARY OF EMPLOYEES</t>
+  </si>
+  <si>
+    <t>6 TOTAL RATING FOR EMPLOYEES</t>
+  </si>
+  <si>
+    <t>7 AVERAGE RATING FOR EMPLOYEES</t>
+  </si>
+  <si>
+    <t>8 MINIMUM RATING FOR EMPLOYEES</t>
+  </si>
+  <si>
+    <t>9 MAXIMUM RATING FOR EMPLOYEES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 AVERAGE SALARY OF EMPLOYEES</t>
+  </si>
+  <si>
+    <t>5  EMPLOYEES RECORDS</t>
+  </si>
+  <si>
+    <t>10 PERFORMANCE RATING RECORDS</t>
   </si>
 </sst>
 </file>
@@ -965,7 +971,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -993,6 +999,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1035,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1058,11 +1088,56 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1083,21 +1158,9 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1267,6 +1330,511 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>358224</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>99084</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F061547-3D6B-39FD-2CF7-29B1C236E088}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="914400"/>
+          <a:ext cx="967824" cy="281964"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>586741</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>160050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD8F19E9-7FFE-8800-BFF1-49845A25539D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828801" y="2011680"/>
+          <a:ext cx="1196340" cy="342930"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>358224</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>137188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F00D7CF1-4FF3-3EDA-E538-1748A00D1039}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="3108960"/>
+          <a:ext cx="967824" cy="320068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>358224</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>121946</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B6A688-237E-11CE-9B9B-440185595210}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4206240"/>
+          <a:ext cx="967824" cy="304826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E626715-BD7B-64FA-27A8-346FF1449FD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="5120640"/>
+          <a:ext cx="1219200" cy="381033"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>464913</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>137188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBBEA6C5-D35F-CFD9-96D5-CCBB56635C9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9288780" y="914400"/>
+          <a:ext cx="1074513" cy="320068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38209</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>175291</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C833076-2F9E-02F2-CC7A-D8EBAC3B46BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9288780" y="2011680"/>
+          <a:ext cx="1257409" cy="358171"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>533499</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>175291</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F5B378F-97B4-8CD5-937D-5B0C7A55739C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9288780" y="3108960"/>
+          <a:ext cx="1143099" cy="358171"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>396327</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>121946</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457E23B2-293D-442C-D027-64C02E170402}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9288780" y="4206240"/>
+          <a:ext cx="1005927" cy="304826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>571602</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>121946</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{788C451C-52C5-F3FB-6164-AFED6933CB5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9288780" y="5120640"/>
+          <a:ext cx="1181202" cy="304826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E2277F7-B24A-4B9E-AC8D-2890DA48D9BC}" name="Table1" displayName="Table1" ref="A1:I151" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14">
   <autoFilter ref="A1:I151" xr:uid="{4E2277F7-B24A-4B9E-AC8D-2890DA48D9BC}"/>
@@ -1286,12 +1854,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89CD202E-D452-4B9A-8C0E-B3249D73BF39}" name="Table2" displayName="Table2" ref="K1:M6" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{89CD202E-D452-4B9A-8C0E-B3249D73BF39}" name="Table2" displayName="Table2" ref="K1:M6" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="K1:M6" xr:uid="{89CD202E-D452-4B9A-8C0E-B3249D73BF39}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B7372CFC-2E4A-4070-A161-84050AA6A436}" name="METRICS" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{BF765DAA-A777-4A07-8F8A-8FA6B996F25F}" name="SALARY" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{A32F279F-4715-4211-AEC4-EC8D14A344B5}" name="PERFOMANCE RATING" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B7372CFC-2E4A-4070-A161-84050AA6A436}" name="METRICS" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{BF765DAA-A777-4A07-8F8A-8FA6B996F25F}" name="SALARY" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A32F279F-4715-4211-AEC4-EC8D14A344B5}" name="PERFOMANCE RATING" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1631,14 +2199,14 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="K1" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1665,14 +2233,14 @@
       <c r="I2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="K2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="L2" s="8">
         <f>SUM(E2:E151)</f>
         <v>9411892</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="8">
         <f>SUM(G2:G151)</f>
         <v>359</v>
       </c>
@@ -1705,14 +2273,14 @@
       <c r="I3" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="K3" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="L3" s="8">
         <f>AVERAGE(E2:E151)</f>
         <v>66280.929577464791</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="8">
         <f>AVERAGE(G2:G151)</f>
         <v>2.8719999999999999</v>
       </c>
@@ -1743,14 +2311,14 @@
       <c r="I4" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="K4" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="L4" s="8">
         <f>MIN(E2:E151)</f>
         <v>30280</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="8">
         <f>MIN(G2:G151)</f>
         <v>1</v>
       </c>
@@ -1783,14 +2351,14 @@
       <c r="I5" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="K5" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" s="8">
         <f>MAX(E2:E151)</f>
         <v>99621</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="8">
         <f>MAX(G2:G151)</f>
         <v>5</v>
       </c>
@@ -1823,14 +2391,14 @@
       <c r="I6" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="L6" s="8">
         <f>COUNT(E2:E151)</f>
         <v>142</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="8">
         <f>COUNT(G2:G151)</f>
         <v>125</v>
       </c>
@@ -5784,56 +6352,120 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D4E995-0299-4C20-ABE5-8C97A582D8AA}">
-  <dimension ref="C3:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76FEA30E-ADD2-4797-A89F-FEE0C6C83193}">
+  <dimension ref="B2:U27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B2" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="10"/>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="H4" s="12">
+        <v>9411892</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="U4" s="12">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="H10" s="12">
+        <v>66280.929999999993</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="U10" s="12">
+        <v>2.8719999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="H16" s="12">
+        <v>30280</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="U16" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B22" s="11" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C9" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="H22" s="12">
+        <v>99621</v>
+      </c>
+      <c r="N22" s="11" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C11" t="s">
-        <v>295</v>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="U22" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B27" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="H27" s="12">
+        <v>142</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="U27" s="12">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>